--- a/meta/en/16-1-1.xlsx
+++ b/meta/en/16-1-1.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" codeName="Workbook________" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDFB2683-6134-4004-9DB5-10CE4FF4E711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист 1" sheetId="2" r:id="rId1"/>
@@ -103,81 +104,77 @@
     <t xml:space="preserve">16.1.1: Number of victims of intentional homicide per 100,000 population, by sex and age </t>
   </si>
   <si>
-    <t>The National Statistical Committee of the Kyrgyz Republic (Demographic Statistics Department)</t>
-  </si>
-  <si>
-    <t>T. S. Taipova</t>
-  </si>
-  <si>
-    <t>t.taipova@stat.kg, tamarataipova@mail.ru</t>
-  </si>
-  <si>
-    <t>(312) 32 46 36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The total count of victims of intentional homicide divided by the total population, expressed per 100,000 population. </t>
-  </si>
-  <si>
-    <t>Intentional homicide is defined as the unlawful death inflicted upon a person with the intent to cause death or serious injury (Source: International Classification of Crime for Statistical Purposes, ICCS 2015).</t>
-  </si>
-  <si>
-    <t>This indicator is widely used at national and international level to measure the most extreme form of violent crime and it also provides a direct indication of lack of security. Security from violence is a prerequisite for individuals to enjoy a safe and active life and for societies and economies to develop freely. Intentional homicides occur in all countries of the world and this indicator has a global applicability.
-Monitoring intentional homicides is necessary to better assess their causes, drivers and consequences and, in the longer term, to develop effective preventive measures. If data are properly disaggregated (as suggested in the ICCS 2015), the indicator can identify the different type of violence associated with homicide: inter-personal (including partner and family-related violence), crime (including organized crime and other forms of criminal activities) and socio-political (including terrorism, hate crime).</t>
-  </si>
-  <si>
-    <t>The source of information on death causes are based on medical records issued by a doctor or paramedic regarding illness, accident, homicide, suicide and other external influences that caused the death. These documents, alongside with the death records, are submitted to the State statistics authorities for further processing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Death data are obtained based on annual statistical compilation from the death records issued by civil registry offices. Aggregate data are collected and processed by the regional statistical offices and the National Statistical Committee (NSC) of the Kyrgyz Republic. </t>
-  </si>
-  <si>
-    <t>The proportion of the total number of victims of intentional homicide recorded in a given year divided by the total resident population in the same year. Calculated per 100,000 population.</t>
-  </si>
-  <si>
-    <t>The ICCS 2015 provides important clarifications on the definition of intentional homicide. In particular, it states that the following killings are included in the count of homicide:
-- Murder
-- Honour killing
-- Serious assault leading to death
-- Death as a result of terrorist activities
-- Dowry-related killings
-- Femicide
-- Infanticide
-- Voluntary manslaughter
-- Extrajudicial killings
-- Killings caused by excessive force by law enforcement/state officials. 
-Furthermore, the ICCS provides indications on how to distinguish between intentional homicides, killings directly related to war/conflict and other killings that amount to war crimes.</t>
-  </si>
-  <si>
-    <t>Logical and arithmetic control of the reported data is performed. Death data verification in death records is carried out through logical control, embedded in the data input and development software. Death codes provided in the death records based on the diagnoses are brought in line with ICD-10. Analysis of output tables by death causes.</t>
-  </si>
-  <si>
-    <t>Data on suicide deaths are published in statistical compendiums “Women and Men in the KR”, “Social trends in the KR”, “Statistical yearbook of the KR”, “Kyrgyzstan in figures”, and are placed at the NSC website.</t>
-  </si>
-  <si>
-    <t>By area – country, oblast, district
-By sex – both genders – mena and women.</t>
-  </si>
-  <si>
-    <t>The national indicator definition used in statistics corresponds to its international definition. Death data are coded and processed according to death causes by the state statistical bodies in line with the International Statistical Classification of Diseases and Causes of Death, 10th revision (ICD-10) of the World Health Organization (WHO) since submission of 2000 Report. As agreed with the NSC, the mortality database is transferred to the eHealth Centre of the Kyrgyz Republic under the Ministry of Health: Form 2 Information on the Number of Births, Marriages, Divorces and Deaths by death causes monthly, with a 1.5 month delay of the reporting month; and Form C52 Mortality by Death Causes annually, in June in the year following the reporting year.</t>
-  </si>
-  <si>
-    <t>The Kyrgyz Republic SDG National Reporting Platform: https://sustainabledevelopment-kyrgyzstan.github.io 
-Links to normative legal acts and methodology: http://www.stat.kg/u/about/pravovye-osnovy-organov-gosudarstvennoj-statistiki/; https://unstats.un.org/sdgs/Metadata; http://www.stat.kg/ru/statistics/download/methodology/68/. The NSC statistical publications: Socio-Economic Status of the Kyrgyz Republic – monthly report; statistical compendiums: Women and Men in the Kyrgyz Republic, Social trends in the Kyrgyz Republic, Public Health and Health Care in the Kyrgyz Republic available at the official NSC KR website: http://www.stat.kg/ru/publications/</t>
-  </si>
-  <si>
-    <t>www.stat.gov.kg</t>
+    <t>aselkarmyshalieva2022@gmail.com</t>
+  </si>
+  <si>
+    <t>(312) 56-70-19 доп.2005</t>
+  </si>
+  <si>
+    <t>www.prokuror.kg</t>
+  </si>
+  <si>
+    <t>Кarmyshalieva А.А.</t>
+  </si>
+  <si>
+    <t>Prosecutor General’s Office of the Kyrgyz Republic</t>
+  </si>
+  <si>
+    <t>The total number of victims of intentional homicide divided by the population, expressed per 100,000 persons</t>
+  </si>
+  <si>
+    <t>Intentional homicide is defined as the unlawful death inflicted upon a person with the intent to cause death or serious injury. (Source: International Classification of Crime for Statistical Purposes, ICCS 2015).</t>
+  </si>
+  <si>
+    <t>This indicator is used to assess the level of the most extreme forms of violence and the state of public safety. Monitoring intentional homicides is necessary to understand their causes and consequences, as well as to develop effective preventive measures and government programs aimed at reducing the level of violence.</t>
+  </si>
+  <si>
+    <t>Unified Register of Crimes of the Prosecutor General’s Office of the Kyrgyz Republic.</t>
+  </si>
+  <si>
+    <t>Administrative data of law enforcement agencies entered by registrars into the UIS “Unified Register of Crimes”.</t>
+  </si>
+  <si>
+    <t>The ratio of the number of deaths resulting from intentional homicide to the average annual resident population, based on the current estimate. It is calculated per 100,000 population.</t>
+  </si>
+  <si>
+    <t>The calculation of the indicator includes crimes initiated under Article 122 of the Criminal Code of the Kyrgyz Republic at the pre-trial stage.</t>
+  </si>
+  <si>
+    <t>Data are regularly cross-checked with the information contained in the UIS “Unified Register of Crimes” in order to ensure their completeness, accuracy, and timeliness.</t>
+  </si>
+  <si>
+    <t>Data are available annually начиная with 2015.</t>
+  </si>
+  <si>
+    <t>Disaggregation is available by territory — republic, oblast, district — and by sex.</t>
+  </si>
+  <si>
+    <t>The data are comparable with those of UNODC and IOM; however, discrepancies may occur due to differences in national recording practices.</t>
+  </si>
+  <si>
+    <t>ICCS 2015
+www.prokuror.kg                                                                                                                                                                                                                                                                                                                                                            UNODC Global Study on Homicide
+ww w.stat.gov.kg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -252,36 +249,40 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -297,9 +298,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -337,9 +338,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -374,7 +375,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -409,7 +410,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -582,7 +583,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Worksheet____1"/>
   <dimension ref="A1:B26"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -633,23 +634,23 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>30</v>
+      <c r="B7" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>31</v>
+      <c r="B8" s="8" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -657,7 +658,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -665,7 +666,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -679,7 +680,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="201.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -687,7 +688,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="408.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -695,7 +696,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -709,7 +710,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -717,7 +718,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -731,7 +732,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="217.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -739,7 +740,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -747,7 +748,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -761,7 +762,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -769,15 +770,15 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="120" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="243.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -785,7 +786,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
